--- a/서버정보/20260716_리소스배포_테스트.xlsx
+++ b/서버정보/20260716_리소스배포_테스트.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zenithn\PowerShell - 리소스 배포\서버정보\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9629E731-DE9E-496E-A17D-C809D29BC7BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8064C0AE-C3CD-4BA2-AD04-9F04F841C524}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3730,10 +3730,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>/subscriptions/b73b1d70-b43f-41b5-bb3f-34b9236d2ed9/resourceGroups/hazr-l-mgmt-rg/providers/Microsoft.Compute/galleries/hazrlmgmtgal/images/RHEL_9.8_Base_Image/versions/0.0.2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>TREU</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -3771,6 +3767,10 @@
   </si>
   <si>
     <t>Default</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>/subscriptions/b73b1d70-b43f-41b5-bb3f-34b9236d2ed9/resourceGroups/hazr-l-mgmt-rg/providers/Microsoft.Compute/galleries/hazrlmgmtgal/images/RHEL_9.8_Base_Image/versions/0.0.3</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -4253,7 +4253,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="115">
+  <cellXfs count="113">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -4592,12 +4592,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -9980,17 +9974,17 @@
     </row>
     <row r="57" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A57" s="84" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="B57" s="84" t="str" cm="1">
         <f t="array" ref="B57">UPPER(INDEX(_xlfn.TEXTSPLIT($C57, "-"), 3))</f>
         <v>BDP</v>
       </c>
       <c r="C57" s="84" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="D57" s="84" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="E57" s="84" t="str">
         <f t="shared" si="20"/>
@@ -10001,7 +9995,7 @@
         <v>t-bdp-rlgcweb-lb-fe</v>
       </c>
       <c r="G57" s="84" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="H57" s="84"/>
       <c r="I57" s="84" t="b">
@@ -10017,14 +10011,14 @@
         <v>t-bdp-rlgcweb-lb-pb</v>
       </c>
       <c r="M57" s="84" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="N57" s="84"/>
       <c r="O57" s="84">
         <v>4</v>
       </c>
       <c r="P57" s="84" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="Q57" s="84" t="b">
         <v>1</v>
@@ -10044,8 +10038,8 @@
       <c r="C58" s="74" t="s">
         <v>375</v>
       </c>
-      <c r="D58" s="114" t="s">
-        <v>570</v>
+      <c r="D58" s="74" t="s">
+        <v>569</v>
       </c>
       <c r="E58" s="74" t="str">
         <f t="shared" ref="E58" si="24">SUBSTITUTE(D58, "hazr-", "")&amp;"-rule"&amp;N58</f>
@@ -14848,7 +14842,7 @@
       <c r="S51" s="107"/>
       <c r="T51" s="107"/>
       <c r="U51" s="107" t="str">
-        <f>SUBSTITUTE(F51,"hazr-","")&amp;"-nic"</f>
+        <f t="shared" ref="U51:U57" si="7">SUBSTITUTE(F51,"hazr-","")&amp;"-nic"</f>
         <v>t-if-icsweb01-nic</v>
       </c>
       <c r="V51" s="107" t="b">
@@ -14920,7 +14914,7 @@
       <c r="M52" s="107" t="s">
         <v>521</v>
       </c>
-      <c r="N52" s="107" t="s">
+      <c r="N52" s="111" t="s">
         <v>546</v>
       </c>
       <c r="O52" s="107" t="str">
@@ -14937,7 +14931,7 @@
       <c r="S52" s="107"/>
       <c r="T52" s="107"/>
       <c r="U52" s="107" t="str">
-        <f>SUBSTITUTE(F52,"hazr-","")&amp;"-nic"</f>
+        <f t="shared" si="7"/>
         <v>t-com-esnweb01-nic</v>
       </c>
       <c r="V52" s="107" t="b">
@@ -15009,7 +15003,7 @@
       <c r="M53" s="107" t="s">
         <v>521</v>
       </c>
-      <c r="N53" s="107" t="s">
+      <c r="N53" s="111" t="s">
         <v>546</v>
       </c>
       <c r="O53" s="107" t="str">
@@ -15026,7 +15020,7 @@
       <c r="S53" s="107"/>
       <c r="T53" s="107"/>
       <c r="U53" s="107" t="str">
-        <f>SUBSTITUTE(F53,"hazr-","")&amp;"-nic"</f>
+        <f t="shared" si="7"/>
         <v>t-com-esnap01-nic</v>
       </c>
       <c r="V53" s="107" t="b">
@@ -15115,7 +15109,7 @@
       <c r="S54" s="107"/>
       <c r="T54" s="107"/>
       <c r="U54" s="107" t="str">
-        <f>SUBSTITUTE(F54,"hazr-","")&amp;"-nic"</f>
+        <f t="shared" si="7"/>
         <v>t-dtg-bbigeoap01-nic</v>
       </c>
       <c r="V54" s="107" t="b">
@@ -15204,7 +15198,7 @@
       <c r="S55" s="107"/>
       <c r="T55" s="107"/>
       <c r="U55" s="107" t="str">
-        <f>SUBSTITUTE(F55,"hazr-","")&amp;"-nic"</f>
+        <f t="shared" si="7"/>
         <v>t-if-hipsap01-nic</v>
       </c>
       <c r="V55" s="107" t="b">
@@ -15245,7 +15239,7 @@
         <f t="array" ref="C56">UPPER(INDEX(_xlfn.TEXTSPLIT($D56, "-"), 3))</f>
         <v>BDP</v>
       </c>
-      <c r="D56" s="113" t="s">
+      <c r="D56" s="107" t="s">
         <v>375</v>
       </c>
       <c r="E56" s="107" t="s">
@@ -15276,9 +15270,9 @@
         <v>521</v>
       </c>
       <c r="N56" s="111" t="s">
-        <v>565</v>
-      </c>
-      <c r="O56" s="113" t="str">
+        <v>575</v>
+      </c>
+      <c r="O56" s="107" t="str">
         <f>SUBSTITUTE(F56,"hazr-","")&amp;"-osdisk"</f>
         <v>t-bdp-rlgcweb01-osdisk</v>
       </c>
@@ -15288,11 +15282,11 @@
       <c r="Q56" s="107" t="s">
         <v>181</v>
       </c>
-      <c r="R56" s="113"/>
+      <c r="R56" s="107"/>
       <c r="S56" s="107"/>
-      <c r="T56" s="113"/>
-      <c r="U56" s="113" t="str">
-        <f>SUBSTITUTE(F56,"hazr-","")&amp;"-nic"</f>
+      <c r="T56" s="107"/>
+      <c r="U56" s="107" t="str">
+        <f t="shared" si="7"/>
         <v>t-bdp-rlgcweb01-nic</v>
       </c>
       <c r="V56" s="107" t="b">
@@ -15333,7 +15327,7 @@
         <f t="array" ref="C57">UPPER(INDEX(_xlfn.TEXTSPLIT($D57, "-"), 3))</f>
         <v>BDP</v>
       </c>
-      <c r="D57" s="113" t="s">
+      <c r="D57" s="107" t="s">
         <v>375</v>
       </c>
       <c r="E57" s="107" t="s">
@@ -15364,9 +15358,9 @@
         <v>521</v>
       </c>
       <c r="N57" s="111" t="s">
-        <v>565</v>
-      </c>
-      <c r="O57" s="113" t="str">
+        <v>575</v>
+      </c>
+      <c r="O57" s="107" t="str">
         <f>SUBSTITUTE(F57,"hazr-","")&amp;"-osdisk"</f>
         <v>t-bdp-rlgcap01-osdisk</v>
       </c>
@@ -15376,15 +15370,15 @@
       <c r="Q57" s="107" t="s">
         <v>181</v>
       </c>
-      <c r="R57" s="113"/>
+      <c r="R57" s="107"/>
       <c r="S57" s="107"/>
-      <c r="T57" s="113"/>
-      <c r="U57" s="113" t="str">
-        <f>SUBSTITUTE(F57,"hazr-","")&amp;"-nic"</f>
+      <c r="T57" s="107"/>
+      <c r="U57" s="107" t="str">
+        <f t="shared" si="7"/>
         <v>t-bdp-rlgcap01-nic</v>
       </c>
       <c r="V57" s="107" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="W57" s="107" t="b">
         <v>1</v>
@@ -18216,7 +18210,7 @@
         <v>524</v>
       </c>
       <c r="G51" s="73" t="str">
-        <f>SUBSTITUTE($F51,"hazr-","")&amp;"-disk01"</f>
+        <f t="shared" ref="G51:G57" si="4">SUBSTITUTE($F51,"hazr-","")&amp;"-disk01"</f>
         <v>t-if-icsweb01-disk01</v>
       </c>
       <c r="H51" s="73" t="s">
@@ -18271,7 +18265,7 @@
         <v>542</v>
       </c>
       <c r="G52" s="74" t="str">
-        <f>SUBSTITUTE($F52,"hazr-","")&amp;"-disk01"</f>
+        <f t="shared" si="4"/>
         <v>t-com-esnweb01-disk01</v>
       </c>
       <c r="H52" s="74" t="s">
@@ -18281,7 +18275,7 @@
         <v>128</v>
       </c>
       <c r="J52" s="74" t="str">
-        <f t="shared" ref="J52:J57" si="4">SUBSTITUTE($F52,"hazr-","")&amp;"-disk02"</f>
+        <f t="shared" ref="J52:J57" si="5">SUBSTITUTE($F52,"hazr-","")&amp;"-disk02"</f>
         <v>t-com-esnweb01-disk02</v>
       </c>
       <c r="K52" s="74" t="s">
@@ -18326,7 +18320,7 @@
         <v>543</v>
       </c>
       <c r="G53" s="73" t="str">
-        <f>SUBSTITUTE($F53,"hazr-","")&amp;"-disk01"</f>
+        <f t="shared" si="4"/>
         <v>t-com-esnwas01-disk01</v>
       </c>
       <c r="H53" s="73" t="s">
@@ -18336,7 +18330,7 @@
         <v>128</v>
       </c>
       <c r="J53" s="73" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>t-com-esnwas01-disk02</v>
       </c>
       <c r="K53" s="73" t="s">
@@ -18380,7 +18374,7 @@
         <v>550</v>
       </c>
       <c r="G54" s="74" t="str">
-        <f>SUBSTITUTE($F54,"hazr-","")&amp;"-disk01"</f>
+        <f t="shared" si="4"/>
         <v>t-dtg-bbigeoap01-disk01</v>
       </c>
       <c r="H54" s="74" t="s">
@@ -18390,7 +18384,7 @@
         <v>128</v>
       </c>
       <c r="J54" s="74" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>t-dtg-bbigeoap01-disk02</v>
       </c>
       <c r="K54" s="74" t="s">
@@ -18435,7 +18429,7 @@
         <v>555</v>
       </c>
       <c r="G55" s="73" t="str">
-        <f>SUBSTITUTE($F55,"hazr-","")&amp;"-disk01"</f>
+        <f t="shared" si="4"/>
         <v>t-if-hipsap01-disk01</v>
       </c>
       <c r="H55" s="73" t="s">
@@ -18445,7 +18439,7 @@
         <v>128</v>
       </c>
       <c r="J55" s="73" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>t-if-hipsap01-disk02</v>
       </c>
       <c r="K55" s="73" t="s">
@@ -18489,7 +18483,7 @@
         <v>559</v>
       </c>
       <c r="G56" s="74" t="str">
-        <f>SUBSTITUTE($F56,"hazr-","")&amp;"-disk01"</f>
+        <f t="shared" si="4"/>
         <v>t-bdp-rlgcweb01-disk01</v>
       </c>
       <c r="H56" s="74" t="s">
@@ -18499,7 +18493,7 @@
         <v>128</v>
       </c>
       <c r="J56" s="74" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>t-bdp-rlgcweb01-disk02</v>
       </c>
       <c r="K56" s="74" t="s">
@@ -18543,7 +18537,7 @@
         <v>561</v>
       </c>
       <c r="G57" s="73" t="str">
-        <f>SUBSTITUTE($F57,"hazr-","")&amp;"-disk01"</f>
+        <f t="shared" si="4"/>
         <v>t-bdp-rlgcap01-disk01</v>
       </c>
       <c r="H57" s="73" t="s">
@@ -18553,7 +18547,7 @@
         <v>1024</v>
       </c>
       <c r="J57" s="73" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>t-bdp-rlgcap01-disk02</v>
       </c>
       <c r="K57" s="73" t="s">
@@ -21442,7 +21436,7 @@
         <v>516</v>
       </c>
       <c r="M74" s="82" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
     </row>
     <row r="75" spans="1:13" x14ac:dyDescent="0.3">
@@ -21483,7 +21477,7 @@
         <v>516</v>
       </c>
       <c r="M75" s="80" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
     </row>
   </sheetData>
@@ -26004,7 +25998,7 @@
     </row>
     <row r="39" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B39" s="84" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="C39" s="84" t="str" cm="1">
         <f t="array" ref="C39">UPPER(INDEX(_xlfn.TEXTSPLIT($F39, "-"), 3))</f>
@@ -26017,7 +26011,7 @@
         <v>24</v>
       </c>
       <c r="F39" s="84" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="G39" s="84" t="s">
         <v>111</v>
@@ -26048,7 +26042,7 @@
         <v>108</v>
       </c>
       <c r="P39" s="84" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="Q39" s="85" t="str">
         <f t="shared" si="3"/>
@@ -26056,32 +26050,32 @@
       </c>
     </row>
     <row r="40" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="B40" s="114" t="s">
-        <v>568</v>
-      </c>
-      <c r="C40" s="114" t="str" cm="1">
+      <c r="B40" s="74" t="s">
+        <v>567</v>
+      </c>
+      <c r="C40" s="74" t="str" cm="1">
         <f t="array" ref="C40">UPPER(INDEX(_xlfn.TEXTSPLIT($F40, "-"), 3))</f>
         <v>BDP</v>
       </c>
-      <c r="D40" s="114" t="s">
+      <c r="D40" s="74" t="s">
         <v>375</v>
       </c>
-      <c r="E40" s="114" t="s">
+      <c r="E40" s="74" t="s">
         <v>24</v>
       </c>
-      <c r="F40" s="114" t="s">
-        <v>570</v>
-      </c>
-      <c r="G40" s="114" t="s">
+      <c r="F40" s="74" t="s">
+        <v>569</v>
+      </c>
+      <c r="G40" s="74" t="s">
         <v>111</v>
       </c>
-      <c r="H40" s="114" t="s">
+      <c r="H40" s="74" t="s">
         <v>538</v>
       </c>
       <c r="I40" s="74" t="s">
         <v>537</v>
       </c>
-      <c r="J40" s="114" t="s">
+      <c r="J40" s="74" t="s">
         <v>102</v>
       </c>
       <c r="K40" s="74" t="str">
@@ -26101,7 +26095,7 @@
         <v>108</v>
       </c>
       <c r="P40" s="74" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="Q40" s="87" t="str">
         <f t="shared" ref="Q40" si="5">SUBSTITUTE(F40, "hazr-", "")&amp;"-bp"</f>
@@ -27929,7 +27923,7 @@
         <v>553</v>
       </c>
       <c r="F56" s="74" t="str">
-        <f t="shared" ref="F56:F57" si="5">SUBSTITUTE(E56, "hazr-", "")&amp;"-pb"&amp;H56</f>
+        <f t="shared" ref="F56" si="5">SUBSTITUTE(E56, "hazr-", "")&amp;"-pb"&amp;H56</f>
         <v>t-dtg-bbigeoap-lb-pb9089</v>
       </c>
       <c r="G56" s="74" t="s">
@@ -27948,21 +27942,21 @@
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B57" s="84" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="C57" s="84" t="str" cm="1">
         <f t="array" ref="C57">UPPER(INDEX(_xlfn.TEXTSPLIT($D57, "-"), 3))</f>
         <v>BDP</v>
       </c>
       <c r="D57" s="84" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="E57" s="84" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="F57" s="84"/>
       <c r="G57" s="84" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="H57" s="84"/>
       <c r="I57" s="84"/>
@@ -27974,18 +27968,18 @@
       </c>
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B58" s="114" t="s">
-        <v>182</v>
-      </c>
-      <c r="C58" s="114" t="str" cm="1">
+      <c r="B58" s="74" t="s">
+        <v>182</v>
+      </c>
+      <c r="C58" s="74" t="str" cm="1">
         <f t="array" ref="C58">UPPER(INDEX(_xlfn.TEXTSPLIT($D58, "-"), 3))</f>
         <v>BDP</v>
       </c>
-      <c r="D58" s="114" t="s">
+      <c r="D58" s="74" t="s">
         <v>375</v>
       </c>
-      <c r="E58" s="114" t="s">
-        <v>570</v>
+      <c r="E58" s="74" t="s">
+        <v>569</v>
       </c>
       <c r="F58" s="74"/>
       <c r="G58" s="74" t="s">
@@ -28007,6 +28001,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="문서" ma:contentTypeID="0x010100589F7F6AEE51BC4C92024CB999111E60" ma:contentTypeVersion="4" ma:contentTypeDescription="새 문서를 만듭니다." ma:contentTypeScope="" ma:versionID="7236b106e1291626cb10ba6ee71a9b94">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="89f0f392-688b-4454-b192-0691f37dc811" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="39d8cc4ddeff20ae29b23e47bf838372" ns2:_="">
     <xsd:import namespace="89f0f392-688b-4454-b192-0691f37dc811"/>
@@ -28150,22 +28159,31 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF093BAC-4385-48E8-8492-BA8C8E7EF612}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="89f0f392-688b-4454-b192-0691f37dc811"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAFDA824-0F2E-4C40-8FCD-BF3D34EF26B3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B942A36D-0DEC-4379-B834-CD4D85F3BBDA}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -28181,28 +28199,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAFDA824-0F2E-4C40-8FCD-BF3D34EF26B3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF093BAC-4385-48E8-8492-BA8C8E7EF612}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="89f0f392-688b-4454-b192-0691f37dc811"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>